--- a/data/base/Backlog_16.xlsx
+++ b/data/base/Backlog_16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{074A7D2C-911C-4CF5-992D-E40BC2CB4A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BFF28E-2228-4E4F-9447-A2C76329D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="30">
   <si>
     <t>Status</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Marcos Silva</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
         <v>46139</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>13</v>
@@ -717,7 +720,7 @@
         <v>46139</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>13</v>
@@ -752,7 +755,7 @@
         <v>46139</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>13</v>
@@ -787,7 +790,7 @@
         <v>46139</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>13</v>
@@ -822,7 +825,7 @@
         <v>46139</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>13</v>
@@ -922,7 +925,7 @@
         <v>46139</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K2" s="12" t="s">
         <v>1</v>
@@ -957,7 +960,7 @@
         <v>46139</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>1</v>
@@ -992,7 +995,7 @@
         <v>46139</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>1</v>
@@ -1062,7 +1065,7 @@
         <v>46139</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>1</v>
@@ -1097,7 +1100,7 @@
         <v>46139</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>1</v>
@@ -1132,7 +1135,7 @@
         <v>46139</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>1</v>
@@ -1167,7 +1170,7 @@
         <v>46139</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>1</v>
@@ -1272,7 +1275,7 @@
         <v>46139</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>1</v>
@@ -1342,7 +1345,7 @@
         <v>46139</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>1</v>
@@ -1377,7 +1380,7 @@
         <v>46139</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>1</v>
@@ -1412,7 +1415,7 @@
         <v>46139</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>1</v>
@@ -1447,7 +1450,7 @@
         <v>46139</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>1</v>
@@ -1552,7 +1555,7 @@
         <v>46139</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>1</v>
@@ -1657,7 +1660,7 @@
         <v>46139</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>1</v>
@@ -1692,7 +1695,7 @@
         <v>46139</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>1</v>
@@ -1727,7 +1730,7 @@
         <v>46139</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>1</v>
